--- a/산출물/99_제출파일/작업분해구조_WBS.xlsx
+++ b/산출물/99_제출파일/작업분해구조_WBS.xlsx
@@ -985,30 +985,30 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1282,7 +1282,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.625" defaultRowHeight="16.9"/>
   <cols>
     <col width="7.5" customWidth="1" style="108" min="1" max="1"/>
-    <col width="67.0625" customWidth="1" style="108" min="2" max="2"/>
+    <col width="95.4375" bestFit="1" customWidth="1" style="108" min="2" max="2"/>
     <col width="6" customWidth="1" style="108" min="3" max="3"/>
     <col width="9.5" customWidth="1" style="108" min="4" max="5"/>
     <col width="8" customWidth="1" style="108" min="6" max="6"/>
@@ -1294,14 +1294,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="108">
-      <c r="A1" s="113" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>작업 분해 구조 (WBS) - 앱인토스 미니앱 「하모니」</t>
         </is>
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1" s="108">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>기간  2026-06-19(금) 13:00 ~ 06-26(금)   ·   최종 발표  6/26(금) 14:00 완료   ·   앱 출시  6/26 정식 전체공개(프로덕션) 출시 완료 · 최종 제출  6/29   ·   작성 2026-06-19 / 갱신 2026-06-28   ·   담당 이상혁(PM) · 검토 곽소정</t>
         </is>
@@ -1325,22 +1325,22 @@
       <c r="O3" s="1" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="108">
-      <c r="A4" s="112" t="inlineStr">
+      <c r="A4" s="111" t="inlineStr">
         <is>
           <t>작업 정보</t>
         </is>
       </c>
-      <c r="H4" s="114" t="inlineStr">
+      <c r="H4" s="113" t="inlineStr">
         <is>
           <t>일정   ( 2026-06-19 금  ~  06-26 금 )</t>
         </is>
       </c>
-      <c r="Q4" s="115" t="inlineStr">
+      <c r="Q4" s="114" t="inlineStr">
         <is>
           <t>전체 진척률</t>
         </is>
       </c>
-      <c r="R4" s="116" t="n"/>
+      <c r="R4" s="115" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1" s="108">
       <c r="A5" s="2" t="inlineStr">
@@ -1426,11 +1426,11 @@
 금</t>
         </is>
       </c>
-      <c r="Q5" s="110">
+      <c r="Q5" s="109">
         <f>SUMPRODUCT(F6:F46,G6:G46)/SUM(F6:F46)</f>
         <v/>
       </c>
-      <c r="R5" s="111" t="n"/>
+      <c r="R5" s="110" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1" s="108">
       <c r="A6" s="9" t="inlineStr">
@@ -1960,14 +1960,14 @@
         </is>
       </c>
       <c r="R17" s="67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S17" s="67" t="n">
         <v>8</v>
       </c>
-      <c r="T17" s="103" t="inlineStr">
-        <is>
-          <t>98%</t>
+      <c r="T17" s="68" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>Android·iOS 실기기 회귀·오디오/카메라 권한(RT-01~15, 9건 아이폰 13·갤럭시 S23 Ultra 육안 성공)</t>
+          <t>Android·iOS 실기기 회귀·오디오/카메라 권한(RT-01~15, 15건 아이폰 13·갤럭시 S23 Ultra 육안 확인(핵심 9건 EV-201~209))</t>
         </is>
       </c>
       <c r="C33" s="36" t="inlineStr">
@@ -2553,7 +2553,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H33" s="64" t="n"/>
       <c r="I33" s="65" t="n"/>
@@ -3201,12 +3201,12 @@
   <cols>
     <col width="38.3125" bestFit="1" customWidth="1" style="108" min="1" max="1"/>
     <col width="40" customWidth="1" style="108" min="2" max="2"/>
-    <col width="41.25" customWidth="1" style="108" min="3" max="3"/>
+    <col width="54.125" bestFit="1" customWidth="1" style="108" min="3" max="3"/>
     <col width="12" customWidth="1" style="108" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="108">
-      <c r="A1" s="107" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>하모니 - 산출물·마일스톤·리스크 (WBS 부속)</t>
         </is>
@@ -3686,7 +3686,7 @@
     <row r="30" ht="27" customHeight="1" s="108">
       <c r="A30" s="105" t="inlineStr">
         <is>
-          <t>실기기 검수 RT 9건 아이폰 13·갤럭시 S23 Ultra 육안 성공(미검증 잔여 RT-01·07·09·13·14·15)</t>
+          <t>실기기 검수 RT 15건 아이폰 13·갤럭시 S23 Ultra 육안 확인(핵심 9건 증빙 EV-201~209, 기본 UX 6건 캡처 없음)</t>
         </is>
       </c>
       <c r="B30" s="99" t="inlineStr">
